--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486529_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486529_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L. SMITH</t>
+          <t>J. BOCCA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3028</v>
+        <v>1.7998</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3997</v>
+        <v>0.9442</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9031</v>
+        <v>0.8556</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.4908</v>
+        <v>0.5512</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.3259</v>
+        <v>-0.7755</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.165</v>
+        <v>1.3268</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.6405</v>
+        <v>0.5537</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.7935</v>
+        <v>-0.7086</v>
       </c>
       <c r="L2" t="n">
-        <v>0.153</v>
+        <v>1.2622</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8504</v>
+        <v>-0.0024</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5324</v>
+        <v>-0.067</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.318</v>
+        <v>0.0645</v>
       </c>
       <c r="P2" t="n">
         <v>0.6525</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1411</v>
+        <v>0.596</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9972</v>
+        <v>0.3906</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1439</v>
+        <v>0.2055</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7395</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8616</v>
+        <v>1.2172</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2601</v>
+        <v>1.7698</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3985</v>
+        <v>-0.5526</v>
       </c>
       <c r="G3" t="n">
         <v>1.7571</v>
@@ -688,13 +688,13 @@
         <v>0.87</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1268</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4747</v>
+        <v>-0.0156</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3479</v>
+        <v>-0.502</v>
       </c>
       <c r="V3" t="n">
         <v>0.1952</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. BOCCA</t>
+          <t>L. SMITH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2295</v>
+        <v>0.9832</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4972</v>
+        <v>-0.5809</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7323</v>
+        <v>1.564</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5512</v>
+        <v>-1.4908</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7755</v>
+        <v>-1.3259</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3268</v>
+        <v>-0.165</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5537</v>
+        <v>-0.6405</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7086</v>
+        <v>-0.7935</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2622</v>
+        <v>0.153</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0024</v>
+        <v>-0.8504</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.067</v>
+        <v>-0.5324</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0645</v>
+        <v>-0.318</v>
       </c>
       <c r="P4" t="n">
         <v>0.6525</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0257</v>
+        <v>1.8215</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0565</v>
+        <v>1.0166</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0822</v>
+        <v>0.8048</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. NIANG BEYE</t>
+          <t>A. SCARIOLO ARES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3059</v>
+        <v>0.92</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6262</v>
+        <v>1.1184</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9321</v>
+        <v>-0.1984</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.6452</v>
+        <v>-0.9067</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.4842</v>
+        <v>-0.7298</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.161</v>
+        <v>-0.1769</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.4554</v>
+        <v>0.0281</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.3989</v>
+        <v>-0.0484</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0566</v>
+        <v>0.0765</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1898</v>
+        <v>-0.9348</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0854</v>
+        <v>-0.6814</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1044</v>
+        <v>-0.2534</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.2175</v>
       </c>
       <c r="R5" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9935</v>
+        <v>0.2394</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0467</v>
+        <v>0.1779</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9468</v>
+        <v>0.0616</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.13</v>
+        <v>0.9347</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. SCARIOLO ARES</t>
+          <t>J. MARTINEZ CABEZUDO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3004</v>
+        <v>-0.1827</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7146</v>
+        <v>0.0605</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4142</v>
+        <v>-0.2432</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9067</v>
+        <v>-0.5955</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7298</v>
+        <v>-0.213</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1769</v>
+        <v>-0.3825</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0281</v>
+        <v>0.0365</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0484</v>
+        <v>0.0365</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0765</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9348</v>
+        <v>-0.632</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6814</v>
+        <v>-0.2495</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2534</v>
+        <v>-0.3825</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3801</v>
+        <v>-0.0222</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2259</v>
+        <v>0.024</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1542</v>
+        <v>-0.0463</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9347</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MARTINEZ CABEZUDO</t>
+          <t>S. NIANG BEYE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2443</v>
+        <v>-0.875</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0605</v>
+        <v>-1.1598</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3049</v>
+        <v>0.2848</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5955</v>
+        <v>-1.6452</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.213</v>
+        <v>-1.4842</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3825</v>
+        <v>-0.161</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0365</v>
+        <v>-1.4554</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0365</v>
+        <v>-1.3989</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.0566</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.632</v>
+        <v>-0.1898</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2495</v>
+        <v>-0.0854</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3825</v>
+        <v>-0.1044</v>
       </c>
       <c r="P7" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R7" t="n">
-        <v>0.435</v>
+        <v>1.305</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0839</v>
+        <v>0.8126</v>
       </c>
       <c r="T7" t="n">
-        <v>0.024</v>
+        <v>0.5131</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1079</v>
+        <v>0.2995</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. BRACEY</t>
+          <t>L. CAPALBO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9188</v>
+        <v>-1.1359</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5693</v>
+        <v>-0.8143</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3495</v>
+        <v>-0.3216</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.4259</v>
+        <v>0.0907</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6848</v>
+        <v>-5.5805</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7411</v>
+        <v>5.6712</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9101</v>
+        <v>1.0783</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7205</v>
+        <v>-3.5698</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1896</v>
+        <v>4.6481</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5158</v>
+        <v>-0.9876</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9643</v>
+        <v>-2.0107</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5514</v>
+        <v>1.0231</v>
       </c>
       <c r="P8" t="n">
         <v>-0.2175</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="R8" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5294</v>
+        <v>-1.0091</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2331</v>
+        <v>-0.5876</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2962</v>
+        <v>-0.4215</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. CAPALBO</t>
+          <t>L. BRACEY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3395</v>
+        <v>-1.9197</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8021</v>
+        <v>-1.7243</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5373</v>
+        <v>-0.1954</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0907</v>
+        <v>-2.4259</v>
       </c>
       <c r="H9" t="n">
-        <v>-5.5805</v>
+        <v>-1.6848</v>
       </c>
       <c r="I9" t="n">
-        <v>5.6712</v>
+        <v>-0.7411</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0783</v>
+        <v>-0.9101</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.5698</v>
+        <v>-0.7205</v>
       </c>
       <c r="L9" t="n">
-        <v>4.6481</v>
+        <v>-0.1896</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9876</v>
+        <v>-1.5158</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.0107</v>
+        <v>-0.9643</v>
       </c>
       <c r="O9" t="n">
-        <v>1.0231</v>
+        <v>-0.5514</v>
       </c>
       <c r="P9" t="n">
         <v>-0.2175</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.2127</v>
+        <v>0.5285</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.5754</v>
+        <v>0.0781</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6373</v>
+        <v>0.4503</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. ARAMBURU LAMY</t>
+          <t>B. VAZQUEZ ARRAIZA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0847</v>
+        <v>-2.0748</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2375</v>
+        <v>-1.9576</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.8471</v>
+        <v>-0.1172</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5044</v>
+        <v>-3.0194</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6024</v>
+        <v>-4.857</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.902</v>
+        <v>1.8376</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1727</v>
+        <v>-2.2653</v>
       </c>
       <c r="K10" t="n">
-        <v>1.241</v>
+        <v>-2.9953</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4136</v>
+        <v>0.73</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3318</v>
+        <v>-0.7541</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.8433</v>
+        <v>-1.8617</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5116000000000001</v>
+        <v>1.1076</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2773</v>
+        <v>-0.2055</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0649</v>
+        <v>0.0277</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2125</v>
+        <v>-0.2331</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5204</v>
+        <v>2.4552</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.4552</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. VAZQUEZ ARRAIZA</t>
+          <t>J. ARAMBURU LAMY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2292</v>
+        <v>-3.023</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9886</v>
+        <v>-0.2375</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2405</v>
+        <v>-2.7855</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.0194</v>
+        <v>-1.5044</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.857</v>
+        <v>-0.6024</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8376</v>
+        <v>-0.902</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.2653</v>
+        <v>-0.1727</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.9953</v>
+        <v>1.241</v>
       </c>
       <c r="L11" t="n">
-        <v>0.73</v>
+        <v>-1.4136</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7541</v>
+        <v>-1.3318</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.8617</v>
+        <v>-1.8433</v>
       </c>
       <c r="O11" t="n">
-        <v>1.1076</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3598</v>
+        <v>-0.2157</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0034</v>
+        <v>-0.0649</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3564</v>
+        <v>-0.1508</v>
       </c>
       <c r="V11" t="n">
-        <v>2.4552</v>
+        <v>-1.5204</v>
       </c>
       <c r="W11" t="n">
-        <v>2.4552</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.3863</v>
+        <v>-7.8841</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.4969</v>
+        <v>-6.1797</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8894</v>
+        <v>-1.7044</v>
       </c>
       <c r="G12" t="n">
         <v>-2.139</v>
@@ -1390,13 +1390,13 @@
         <v>0.6525</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2022</v>
+        <v>-0.7</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6934</v>
+        <v>-0.3761</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5088</v>
+        <v>-0.3239</v>
       </c>
       <c r="V12" t="n">
         <v>-1.13</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-13.2026</v>
+        <v>-12.175</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.788499999999999</v>
+        <v>-8.761199999999999</v>
       </c>
       <c r="F13" t="n">
         <v>-3.4139</v>
@@ -1441,16 +1441,16 @@
         <v>6.904699999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.305599999999999</v>
+        <v>-2.3056</v>
       </c>
       <c r="K13" t="n">
-        <v>-6.4296</v>
+        <v>-6.429600000000001</v>
       </c>
       <c r="L13" t="n">
         <v>4.123900000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-9.022399999999999</v>
+        <v>-9.022400000000001</v>
       </c>
       <c r="N13" t="n">
         <v>-11.8032</v>
@@ -1468,13 +1468,13 @@
         <v>8.699999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3005</v>
+        <v>1.3279</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1562000000000006</v>
+        <v>1.1838</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1440999999999998</v>
+        <v>0.1440999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-9.999999999976694e-05</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.5147</v>
+        <v>6.103</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9166</v>
+        <v>3.1401</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5981</v>
+        <v>2.9629</v>
       </c>
       <c r="G14" t="n">
         <v>1.2339</v>
@@ -1546,13 +1546,13 @@
         <v>1.9576</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0633</v>
+        <v>0.6516</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2091</v>
+        <v>0.4326</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1458</v>
+        <v>0.219</v>
       </c>
       <c r="V14" t="n">
         <v>2.2599</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.0677</v>
+        <v>5.5802</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5261</v>
+        <v>3.6378</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5417</v>
+        <v>1.9424</v>
       </c>
       <c r="G15" t="n">
         <v>2.7081</v>
@@ -1624,13 +1624,13 @@
         <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2929</v>
+        <v>0.2196</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3461</v>
+        <v>0.4579</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6389</v>
+        <v>-0.2382</v>
       </c>
       <c r="V15" t="n">
         <v>1.13</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.5648</v>
+        <v>3.9102</v>
       </c>
       <c r="E16" t="n">
-        <v>2.572</v>
+        <v>2.0132</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9928</v>
+        <v>1.8971</v>
       </c>
       <c r="G16" t="n">
         <v>3.2908</v>
@@ -1702,13 +1702,13 @@
         <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4915</v>
+        <v>0.837</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8857</v>
+        <v>0.3269</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3942</v>
+        <v>0.5101</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. NGOM</t>
+          <t>J. TATE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4577</v>
+        <v>1.5606</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4309</v>
+        <v>0.496</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8886</v>
+        <v>1.0645</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1893</v>
+        <v>2.7236</v>
       </c>
       <c r="H17" t="n">
-        <v>1.767</v>
+        <v>3.6192</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5777</v>
+        <v>-0.8957000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4101</v>
+        <v>2.0703</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3719</v>
+        <v>2.7771</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0382</v>
+        <v>-0.7068</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2208</v>
+        <v>0.6533</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3951</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.616</v>
+        <v>-0.1889</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6525</v>
+        <v>1.9576</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0515</v>
+        <v>-0.7078</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3341</v>
+        <v>-0.4867</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7174</v>
+        <v>-0.2211</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7395</v>
+        <v>-1.3252</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.7395</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. TATE</t>
+          <t>A. NGOM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6807</v>
+        <v>1.2613</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1608</v>
+        <v>-0.7661</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5199</v>
+        <v>2.0274</v>
       </c>
       <c r="G18" t="n">
-        <v>2.7236</v>
+        <v>1.1893</v>
       </c>
       <c r="H18" t="n">
-        <v>3.6192</v>
+        <v>1.767</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8957000000000001</v>
+        <v>-0.5777</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0703</v>
+        <v>1.4101</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7771</v>
+        <v>1.3719</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7068</v>
+        <v>0.0382</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6533</v>
+        <v>-0.2208</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.3951</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1889</v>
+        <v>-0.616</v>
       </c>
       <c r="P18" t="n">
-        <v>0.87</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9576</v>
+        <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5877</v>
+        <v>0.855</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.822</v>
+        <v>-0.0012</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7657</v>
+        <v>0.8562</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.3252</v>
+        <v>0.7395</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.3252</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5137</v>
+        <v>1.1392</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1718</v>
+        <v>0.2836</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3418</v>
+        <v>0.8556</v>
       </c>
       <c r="G19" t="n">
         <v>0.0495</v>
@@ -1936,13 +1936,13 @@
         <v>0.435</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2244</v>
+        <v>0.8499</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1971</v>
+        <v>0.3088</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0273</v>
+        <v>0.5411</v>
       </c>
       <c r="V19" t="n">
         <v>-0.1952</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. ANSORREGUI DEBA</t>
+          <t>A. ANABITARTE SOROA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.322</v>
+        <v>0.2004</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3937</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7157</v>
+        <v>0.2004</v>
       </c>
       <c r="G20" t="n">
-        <v>2.0945</v>
+        <v>0.149</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4418</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6526</v>
+        <v>0.149</v>
       </c>
       <c r="J20" t="n">
-        <v>2.807</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4356</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>2.3715</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7126</v>
+        <v>0.149</v>
       </c>
       <c r="N20" t="n">
-        <v>1.0063</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7188</v>
+        <v>0.149</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.9576</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.305</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1198</v>
+        <v>0.0514</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1334</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.2532</v>
+        <v>0.0514</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9347</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. ANABITARTE SOROA</t>
+          <t>M. ANSORREGUI DEBA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1696</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>-0.729</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1696</v>
+        <v>0.2174</v>
       </c>
       <c r="G21" t="n">
-        <v>0.149</v>
+        <v>2.0945</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1.4418</v>
       </c>
       <c r="I21" t="n">
-        <v>0.149</v>
+        <v>0.6526</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>2.807</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.4356</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.3715</v>
       </c>
       <c r="M21" t="n">
-        <v>0.149</v>
+        <v>-0.7126</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.0063</v>
       </c>
       <c r="O21" t="n">
-        <v>0.149</v>
+        <v>-1.7188</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.305</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0205</v>
+        <v>0.2863</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>-0.4687</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0205</v>
+        <v>0.7549</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.9347</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.8032</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8978</v>
+        <v>-1.786</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1574</v>
+        <v>0.9828</v>
       </c>
       <c r="G22" t="n">
         <v>0.6292</v>
@@ -2170,13 +2170,13 @@
         <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5221</v>
+        <v>0.4593</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.1034</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5305</v>
+        <v>0.356</v>
       </c>
       <c r="V22" t="n">
         <v>-1.6743</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2615</v>
+        <v>-1.038</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9326</v>
+        <v>-1.7091</v>
       </c>
       <c r="F23" t="n">
         <v>0.6712</v>
@@ -2248,10 +2248,10 @@
         <v>1.0875</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5275</v>
+        <v>-0.304</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4675</v>
+        <v>-0.2439</v>
       </c>
       <c r="U23" t="n">
         <v>-0.0601</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0865</v>
+        <v>-1.2195</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.2782</v>
+        <v>-1.1664</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8083</v>
+        <v>-0.0531</v>
       </c>
       <c r="G24" t="n">
         <v>-0.9184</v>
@@ -2326,13 +2326,13 @@
         <v>0.2175</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3856</v>
+        <v>-0.5185</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.5732</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7006</v>
+        <v>0.0547</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>13.2025</v>
+        <v>16.1826</v>
       </c>
       <c r="E25" t="n">
-        <v>3.4141</v>
+        <v>3.414099999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>9.788499999999999</v>
+        <v>12.7686</v>
       </c>
       <c r="G25" t="n">
         <v>11.328</v>
       </c>
       <c r="H25" t="n">
-        <v>18.23269999999999</v>
+        <v>18.2327</v>
       </c>
       <c r="I25" t="n">
         <v>-6.9048</v>
@@ -2392,7 +2392,7 @@
         <v>6.429500000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>-4.124000000000001</v>
+        <v>-4.124</v>
       </c>
       <c r="P25" t="n">
         <v>2.175</v>
@@ -2404,16 +2404,16 @@
         <v>10.8752</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3006</v>
+        <v>2.6798</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1442000000000001</v>
+        <v>-0.1441000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1564000000000001</v>
+        <v>2.824</v>
       </c>
       <c r="V25" t="n">
-        <v>6.661338147750939e-16</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="W25" t="n">
         <v>3.236</v>
